--- a/input/sample_document.xlsx
+++ b/input/sample_document.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,9 +28,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,10 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -463,17 +460,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Bob Martinez</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>john.smith@acme.com</t>
+          <t>bob.martinez@acme.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+1-212-555-0141</t>
+          <t>(555) 345-6789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,88 +482,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sarah Mitchell</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sarah.mitchell@acme.com</t>
+          <t>alice.johnson@acme.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+1-415-555-0192</t>
+          <t>(555) 234-5678</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linda Zhao</t>
+          <t>Carol White</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>linda.zhao@acme.com</t>
+          <t>carol.white@acme.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+1-650-555-0173</t>
+          <t>(555) 456-7890</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Robert Huang</t>
+          <t>David Lee</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>r.huang@acme.com</t>
+          <t>david.lee@acme.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1-312-555-0108</t>
+          <t>(555) 567-8901</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alice Pemberley</t>
+          <t>Emma Davis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alice.pemberley@acme.com</t>
+          <t>emma.davis@acme.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1-617-555-0155</t>
+          <t>(555) 678-9012</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -584,29 +581,29 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ProjectName</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -620,61 +617,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kevin Tran</t>
+          <t>Bob Martinez</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,250,000</t>
+          <t>$450,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Prod deployment on PROD-DB-01. API key: sk-prod-aBcD1234eFgH5678iJkL</t>
+          <t>Deploying TIGERS on PROD-DB-01. Approved by Acme Corporation board.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIGERS Integration</t>
+          <t>eReporting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sarah Mitchell</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$340,000</t>
+          <t>$120,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>eReporting module dependency. Contact sarah.mitchell@acme.com for access.</t>
+          <t>Integration with Acme Corporation legacy finance system. Due Q2 2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compliance Refresh</t>
+          <t>Data Migration</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alice Pemberley</t>
+          <t>Carol White</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$95,000</t>
+          <t>$85,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Initiated by Acme Corporation legal team. SSN audit complete.</t>
+          <t>API key for staging access: sk-a1b2c3d4e5f6g7h8. Contact: bob.martinez@acme.com</t>
         </is>
       </c>
     </row>
